--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194278</v>
+        <v>131194271</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598630</v>
+        <v>598541</v>
       </c>
       <c r="R3" t="n">
-        <v>6942814</v>
+        <v>6942916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall. hela stammen full</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194271</v>
+        <v>131194278</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598541</v>
+        <v>598630</v>
       </c>
       <c r="R4" t="n">
-        <v>6942916</v>
+        <v>6942814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på tall. hela stammen full</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1862,7 +1862,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194282</v>
+        <v>131194290</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598601</v>
+        <v>598460</v>
       </c>
       <c r="R12" t="n">
-        <v>6942680</v>
+        <v>6942693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,7 +1982,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194290</v>
+        <v>131194254</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598460</v>
+        <v>598459</v>
       </c>
       <c r="R13" t="n">
-        <v>6942693</v>
+        <v>6942760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,7 +2102,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194254</v>
+        <v>131194292</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598459</v>
+        <v>598490</v>
       </c>
       <c r="R14" t="n">
-        <v>6942760</v>
+        <v>6942625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2222,7 +2222,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194292</v>
+        <v>131194282</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598490</v>
+        <v>598601</v>
       </c>
       <c r="R15" t="n">
-        <v>6942625</v>
+        <v>6942680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2569,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,34 +2580,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R18" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2657,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,42 +2700,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R19" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,7 +2759,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,12 +2769,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194286</v>
+        <v>131194275</v>
       </c>
       <c r="B22" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,33 +3047,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3083,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598570</v>
+        <v>598499</v>
       </c>
       <c r="R22" t="n">
-        <v>6942714</v>
+        <v>6942841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3118,7 +3114,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3128,7 +3124,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,29 +3167,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3198,10 +3203,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R23" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3233,7 +3238,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3243,12 +3248,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3275,7 +3275,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131194272</v>
+        <v>131194276</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>598518</v>
+        <v>598566</v>
       </c>
       <c r="R24" t="n">
-        <v>6942861</v>
+        <v>6942801</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Typiskt bohål av tretåig hackspett. Utifrån att det fortfarande är en hel del kåda kvar runt hålet, lägger jag in det som färska spår, men bohålet är nog i vart fall några år gammalt. 1.5 meter ovan mark i gran. Innerdiametern omkring 4,5 cm vilket mättes med måttband.</t>
+          <t>färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194276</v>
+        <v>131194284</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>598566</v>
+        <v>598593</v>
       </c>
       <c r="R25" t="n">
-        <v>6942801</v>
+        <v>6942660</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färskt ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,10 +3515,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194284</v>
+        <v>131194255</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,42 +3526,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>598593</v>
+        <v>598556</v>
       </c>
       <c r="R26" t="n">
-        <v>6942660</v>
+        <v>6942987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3593,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3603,12 +3595,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3635,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194255</v>
+        <v>131194272</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,34 +3633,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598556</v>
+        <v>598518</v>
       </c>
       <c r="R27" t="n">
-        <v>6942987</v>
+        <v>6942861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3705,7 +3700,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3715,7 +3710,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Typiskt bohål av tretåig hackspett. 1.5 meter ovan mark i gran. Innerdiametern omkring 4,5 cm vilket mättes med måttband.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,42 +1646,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R10" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,12 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B11" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,34 +1753,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R11" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2462,32 +2462,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194289</v>
+        <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>75349</v>
+        <v>79244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598468</v>
+        <v>598597</v>
       </c>
       <c r="R17" t="n">
-        <v>6942694</v>
+        <v>6942768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194281</v>
+        <v>131194285</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,34 +2700,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598597</v>
+        <v>598601</v>
       </c>
       <c r="R19" t="n">
-        <v>6942768</v>
+        <v>6942696</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2759,7 +2767,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2769,7 +2777,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,7 +2809,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131194285</v>
+        <v>131194288</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2839,10 +2852,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598601</v>
+        <v>598546</v>
       </c>
       <c r="R20" t="n">
-        <v>6942696</v>
+        <v>6942727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2874,7 +2887,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2884,7 +2897,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2916,7 +2929,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194288</v>
+        <v>131194275</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2959,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598546</v>
+        <v>598499</v>
       </c>
       <c r="R21" t="n">
-        <v>6942727</v>
+        <v>6942841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +3017,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3036,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,29 +3060,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3079,10 +3096,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R22" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3131,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3124,12 +3141,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,10 +3168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131194286</v>
+        <v>131194276</v>
       </c>
       <c r="B23" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,33 +3179,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3203,10 +3211,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>598570</v>
+        <v>598566</v>
       </c>
       <c r="R23" t="n">
-        <v>6942714</v>
+        <v>6942801</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3275,7 +3288,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131194276</v>
+        <v>131194284</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3318,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>598566</v>
+        <v>598593</v>
       </c>
       <c r="R24" t="n">
-        <v>6942801</v>
+        <v>6942660</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3353,7 +3366,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3363,12 +3376,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färskt ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194284</v>
+        <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3406,42 +3419,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>598593</v>
+        <v>598556</v>
       </c>
       <c r="R25" t="n">
-        <v>6942660</v>
+        <v>6942987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3473,7 +3478,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3483,12 +3488,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,10 +3515,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194255</v>
+        <v>131194272</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,34 +3526,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>598556</v>
+        <v>598518</v>
       </c>
       <c r="R26" t="n">
-        <v>6942987</v>
+        <v>6942861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3585,7 +3593,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,7 +3603,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Typiskt bohål av tretåig hackspett. 1.5 meter ovan mark i gran. Innerdiametern omkring 4,5 cm vilket mättes med måttband.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,53 +3635,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194272</v>
+        <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>75350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598518</v>
+        <v>598468</v>
       </c>
       <c r="R27" t="n">
-        <v>6942861</v>
+        <v>6942694</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3700,7 +3705,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3710,12 +3715,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Typiskt bohål av tretåig hackspett. 1.5 meter ovan mark i gran. Innerdiametern omkring 4,5 cm vilket mättes med måttband.</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B10" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,34 +1646,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R10" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1713,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1723,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,42 +1766,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R11" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,34 +2473,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R17" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,42 +2593,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R18" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194271</v>
+        <v>131194278</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598541</v>
+        <v>598630</v>
       </c>
       <c r="R3" t="n">
-        <v>6942916</v>
+        <v>6942814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på tall. hela stammen full</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194278</v>
+        <v>131194271</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598630</v>
+        <v>598541</v>
       </c>
       <c r="R4" t="n">
-        <v>6942814</v>
+        <v>6942916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall. hela stammen full</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,42 +1646,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R10" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,12 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B11" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,34 +1753,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R11" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,42 +2473,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R17" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,34 +2580,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R18" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2657,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194280</v>
+        <v>131194271</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598625</v>
+        <v>598541</v>
       </c>
       <c r="R2" t="n">
-        <v>6942808</v>
+        <v>6942916</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194278</v>
+        <v>131194280</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598630</v>
+        <v>598625</v>
       </c>
       <c r="R3" t="n">
-        <v>6942814</v>
+        <v>6942808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall. hela stammen full</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194271</v>
+        <v>131194278</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598541</v>
+        <v>598630</v>
       </c>
       <c r="R4" t="n">
-        <v>6942916</v>
+        <v>6942814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på tall. hela stammen full</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1982,7 +1982,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194254</v>
+        <v>131194287</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598459</v>
+        <v>598559</v>
       </c>
       <c r="R13" t="n">
-        <v>6942760</v>
+        <v>6942723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2342,7 +2342,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194287</v>
+        <v>131194254</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598559</v>
+        <v>598459</v>
       </c>
       <c r="R16" t="n">
-        <v>6942723</v>
+        <v>6942760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194271</v>
+        <v>131194280</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598541</v>
+        <v>598625</v>
       </c>
       <c r="R2" t="n">
-        <v>6942916</v>
+        <v>6942808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194280</v>
+        <v>131194271</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598625</v>
+        <v>598541</v>
       </c>
       <c r="R3" t="n">
-        <v>6942808</v>
+        <v>6942916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1638,7 +1638,7 @@
         <v>131194293</v>
       </c>
       <c r="B10" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194287</v>
+        <v>131194254</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598559</v>
+        <v>598459</v>
       </c>
       <c r="R13" t="n">
-        <v>6942723</v>
+        <v>6942760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2342,7 +2342,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194254</v>
+        <v>131194287</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598459</v>
+        <v>598559</v>
       </c>
       <c r="R16" t="n">
-        <v>6942760</v>
+        <v>6942723</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2465,7 +2465,7 @@
         <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75350</v>
+        <v>75351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,34 +2473,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R17" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,42 +2593,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R18" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>131194293</v>
       </c>
       <c r="B10" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,42 +2473,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R17" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,34 +2580,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R18" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2657,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75351</v>
+        <v>75352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B10" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,34 +1646,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R10" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1713,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1723,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,42 +1766,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R11" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194280</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194271</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194278</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194279</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194277</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194291</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194270</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194273</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>131194283</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>131194293</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>131194290</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131194254</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131194292</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>131194282</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>131194287</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>131194285</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131194288</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>131194275</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>131194286</v>
       </c>
       <c r="B22" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>131194276</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131194284</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>131194272</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75352</v>
+        <v>75354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194280</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194271</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194278</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194279</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194277</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194291</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194270</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194273</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,42 +1646,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R10" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,12 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B11" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,34 +1753,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R11" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1865,7 @@
         <v>131194290</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131194254</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131194292</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>131194282</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>131194287</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>131194285</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131194288</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>58046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,29 +2940,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R21" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3007,7 +3011,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,12 +3021,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194286</v>
+        <v>131194275</v>
       </c>
       <c r="B22" t="n">
-        <v>58045</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,33 +3059,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598570</v>
+        <v>598499</v>
       </c>
       <c r="R22" t="n">
-        <v>6942714</v>
+        <v>6942841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3131,7 +3126,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3141,7 +3136,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,7 +3171,7 @@
         <v>131194276</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131194284</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>131194272</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75354</v>
+        <v>75355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,34 +2473,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R17" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,42 +2593,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R18" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194286</v>
+        <v>131194275</v>
       </c>
       <c r="B21" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,33 +2940,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598570</v>
+        <v>598499</v>
       </c>
       <c r="R21" t="n">
-        <v>6942714</v>
+        <v>6942841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3011,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3021,7 +3017,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,29 +3060,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R22" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3126,7 +3131,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3136,12 +3141,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194280</v>
+        <v>131194271</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598625</v>
+        <v>598541</v>
       </c>
       <c r="R2" t="n">
-        <v>6942808</v>
+        <v>6942916</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194271</v>
+        <v>131194280</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598541</v>
+        <v>598625</v>
       </c>
       <c r="R3" t="n">
-        <v>6942916</v>
+        <v>6942808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -918,7 +918,7 @@
         <v>131194278</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194279</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194277</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194291</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194270</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194273</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B10" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,34 +1646,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R10" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1713,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1723,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,42 +1766,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R11" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194290</v>
+        <v>131194282</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598460</v>
+        <v>598601</v>
       </c>
       <c r="R12" t="n">
-        <v>6942693</v>
+        <v>6942680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194254</v>
+        <v>131194292</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598459</v>
+        <v>598490</v>
       </c>
       <c r="R13" t="n">
-        <v>6942760</v>
+        <v>6942625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2102,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194292</v>
+        <v>131194290</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598490</v>
+        <v>598460</v>
       </c>
       <c r="R14" t="n">
-        <v>6942625</v>
+        <v>6942693</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194282</v>
+        <v>131194254</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598601</v>
+        <v>598459</v>
       </c>
       <c r="R15" t="n">
-        <v>6942680</v>
+        <v>6942760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2345,7 +2345,7 @@
         <v>131194287</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>131194274</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>131194281</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>131194285</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131194288</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>131194275</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>131194286</v>
       </c>
       <c r="B22" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>131194276</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131194284</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>131194272</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75355</v>
+        <v>75356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194271</v>
+        <v>131194280</v>
       </c>
       <c r="B2" t="n">
         <v>57888</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598541</v>
+        <v>598625</v>
       </c>
       <c r="R2" t="n">
-        <v>6942916</v>
+        <v>6942808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194280</v>
+        <v>131194271</v>
       </c>
       <c r="B3" t="n">
         <v>57888</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598625</v>
+        <v>598541</v>
       </c>
       <c r="R3" t="n">
-        <v>6942808</v>
+        <v>6942916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1862,7 +1862,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194282</v>
+        <v>131194290</v>
       </c>
       <c r="B12" t="n">
         <v>57888</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598601</v>
+        <v>598460</v>
       </c>
       <c r="R12" t="n">
-        <v>6942680</v>
+        <v>6942693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,7 +1982,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194292</v>
+        <v>131194254</v>
       </c>
       <c r="B13" t="n">
         <v>57888</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598490</v>
+        <v>598459</v>
       </c>
       <c r="R13" t="n">
-        <v>6942625</v>
+        <v>6942760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2102,7 +2102,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194290</v>
+        <v>131194292</v>
       </c>
       <c r="B14" t="n">
         <v>57888</v>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598460</v>
+        <v>598490</v>
       </c>
       <c r="R14" t="n">
-        <v>6942693</v>
+        <v>6942625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,7 +2222,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194254</v>
+        <v>131194282</v>
       </c>
       <c r="B15" t="n">
         <v>57888</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598459</v>
+        <v>598601</v>
       </c>
       <c r="R15" t="n">
-        <v>6942760</v>
+        <v>6942680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,42 +2473,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R17" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,34 +2580,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R18" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2657,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -2929,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>58047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,29 +2940,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R21" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3007,7 +3011,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,12 +3021,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194286</v>
+        <v>131194275</v>
       </c>
       <c r="B22" t="n">
-        <v>58047</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,33 +3059,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598570</v>
+        <v>598499</v>
       </c>
       <c r="R22" t="n">
-        <v>6942714</v>
+        <v>6942841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3131,7 +3126,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3141,7 +3136,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194280</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194271</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194278</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194279</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194277</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194291</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194270</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194273</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>131194283</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>131194293</v>
       </c>
       <c r="B11" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>131194290</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131194254</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>131194292</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>131194282</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>131194287</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,34 +2473,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R17" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,42 +2593,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R18" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2652,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2662,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194285</v>
+        <v>131194288</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598601</v>
+        <v>598546</v>
       </c>
       <c r="R19" t="n">
-        <v>6942696</v>
+        <v>6942727</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2809,10 +2809,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131194288</v>
+        <v>131194285</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598546</v>
+        <v>598601</v>
       </c>
       <c r="R20" t="n">
-        <v>6942727</v>
+        <v>6942696</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194286</v>
+        <v>131194275</v>
       </c>
       <c r="B21" t="n">
-        <v>58047</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,33 +2940,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598570</v>
+        <v>598499</v>
       </c>
       <c r="R21" t="n">
-        <v>6942714</v>
+        <v>6942841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3011,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3021,7 +3017,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>58050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,29 +3060,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R22" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3126,7 +3131,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3136,12 +3141,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,7 +3171,7 @@
         <v>131194276</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131194284</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>131194272</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75356</v>
+        <v>75359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194280</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194271</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194278</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194279</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>131194277</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>131194291</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131194270</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131194273</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194283</v>
+        <v>131194293</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>80359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,42 +1646,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598603</v>
+        <v>598432</v>
       </c>
       <c r="R10" t="n">
-        <v>6942663</v>
+        <v>6942627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,12 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194293</v>
+        <v>131194283</v>
       </c>
       <c r="B11" t="n">
-        <v>80358</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,34 +1753,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598432</v>
+        <v>598603</v>
       </c>
       <c r="R11" t="n">
-        <v>6942627</v>
+        <v>6942663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1830,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194290</v>
+        <v>131194282</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598460</v>
+        <v>598601</v>
       </c>
       <c r="R12" t="n">
-        <v>6942693</v>
+        <v>6942680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194254</v>
+        <v>131194287</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598459</v>
+        <v>598559</v>
       </c>
       <c r="R13" t="n">
-        <v>6942760</v>
+        <v>6942723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2102,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194292</v>
+        <v>131194290</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598490</v>
+        <v>598460</v>
       </c>
       <c r="R14" t="n">
-        <v>6942625</v>
+        <v>6942693</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194282</v>
+        <v>131194254</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598601</v>
+        <v>598459</v>
       </c>
       <c r="R15" t="n">
-        <v>6942680</v>
+        <v>6942760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194287</v>
+        <v>131194292</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598559</v>
+        <v>598490</v>
       </c>
       <c r="R16" t="n">
-        <v>6942723</v>
+        <v>6942625</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194274</v>
+        <v>131194281</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,42 +2473,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598512</v>
+        <v>598597</v>
       </c>
       <c r="R17" t="n">
-        <v>6942845</v>
+        <v>6942768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194281</v>
+        <v>131194274</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,34 +2580,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598597</v>
+        <v>598512</v>
       </c>
       <c r="R18" t="n">
-        <v>6942768</v>
+        <v>6942845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2662,7 +2657,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,7 +2692,7 @@
         <v>131194288</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>131194285</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194275</v>
+        <v>131194286</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>58051</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,29 +2940,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598499</v>
+        <v>598570</v>
       </c>
       <c r="R21" t="n">
-        <v>6942841</v>
+        <v>6942714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3007,7 +3011,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,12 +3021,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194286</v>
+        <v>131194275</v>
       </c>
       <c r="B22" t="n">
-        <v>58050</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,33 +3059,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3096,10 +3091,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598570</v>
+        <v>598499</v>
       </c>
       <c r="R22" t="n">
-        <v>6942714</v>
+        <v>6942841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3131,7 +3126,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3141,7 +3136,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,7 +3171,7 @@
         <v>131194276</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>131194284</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>131194255</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>131194272</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>131194289</v>
       </c>
       <c r="B27" t="n">
-        <v>75359</v>
+        <v>75360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194271</v>
+        <v>131194255</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598541</v>
+        <v>598556</v>
       </c>
       <c r="R2" t="n">
-        <v>6942916</v>
+        <v>6942987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,53 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194280</v>
+        <v>131194281</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598625</v>
+        <v>598597</v>
       </c>
       <c r="R3" t="n">
-        <v>6942808</v>
+        <v>6942768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194278</v>
+        <v>131194289</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598630</v>
+        <v>598468</v>
       </c>
       <c r="R4" t="n">
-        <v>6942814</v>
+        <v>6942694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall. hela stammen full</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194279</v>
+        <v>131194293</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598621</v>
+        <v>598432</v>
       </c>
       <c r="R5" t="n">
-        <v>6942815</v>
+        <v>6942627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack på tall</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194277</v>
+        <v>131194254</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598597</v>
+        <v>598459</v>
       </c>
       <c r="R6" t="n">
-        <v>6942813</v>
+        <v>6942760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194291</v>
+        <v>131194268</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598491</v>
+        <v>598698</v>
       </c>
       <c r="R7" t="n">
-        <v>6942633</v>
+        <v>6943065</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1301,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1311,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska ringhack på tall. hela stammen full</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131194270</v>
+        <v>131194269</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1376,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1438,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598613</v>
+        <v>598689</v>
       </c>
       <c r="R8" t="n">
-        <v>6942984</v>
+        <v>6943069</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131194273</v>
+        <v>131194270</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598517</v>
+        <v>598613</v>
       </c>
       <c r="R9" t="n">
-        <v>6942858</v>
+        <v>6942984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1635,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131194293</v>
+        <v>131194271</v>
       </c>
       <c r="B10" t="n">
-        <v>80365</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,34 +1594,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598432</v>
+        <v>598541</v>
       </c>
       <c r="R10" t="n">
-        <v>6942627</v>
+        <v>6942916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1671,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131194283</v>
+        <v>131194272</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1736,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1785,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598603</v>
+        <v>598518</v>
       </c>
       <c r="R11" t="n">
-        <v>6942663</v>
+        <v>6942861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1791,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>Typiskt bohål av tretåig hackspett. 1.5 meter ovan mark i gran. Innerdiametern omkring 4,5 cm vilket mättes med måttband.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131194254</v>
+        <v>131194273</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598459</v>
+        <v>598517</v>
       </c>
       <c r="R12" t="n">
-        <v>6942760</v>
+        <v>6942858</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1982,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131194282</v>
+        <v>131194274</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598601</v>
+        <v>598512</v>
       </c>
       <c r="R13" t="n">
-        <v>6942680</v>
+        <v>6942845</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2102,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131194287</v>
+        <v>131194275</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598559</v>
+        <v>598499</v>
       </c>
       <c r="R14" t="n">
-        <v>6942723</v>
+        <v>6942841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2222,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131194290</v>
+        <v>131194276</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598460</v>
+        <v>598566</v>
       </c>
       <c r="R15" t="n">
-        <v>6942693</v>
+        <v>6942801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,12 +2271,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131194292</v>
+        <v>131194277</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598490</v>
+        <v>598597</v>
       </c>
       <c r="R16" t="n">
-        <v>6942625</v>
+        <v>6942813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2462,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131194281</v>
+        <v>131194278</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,34 +2434,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598597</v>
+        <v>598630</v>
       </c>
       <c r="R17" t="n">
-        <v>6942768</v>
+        <v>6942814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,7 +2511,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall. hela stammen full</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,10 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131194274</v>
+        <v>131194279</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2576,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2612,10 +2586,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598512</v>
+        <v>598621</v>
       </c>
       <c r="R18" t="n">
-        <v>6942845</v>
+        <v>6942815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2631,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131194285</v>
+        <v>131194280</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,10 +2706,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598601</v>
+        <v>598625</v>
       </c>
       <c r="R19" t="n">
-        <v>6942696</v>
+        <v>6942808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2767,7 +2741,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2777,7 +2751,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2809,10 +2783,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131194288</v>
+        <v>131194282</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598546</v>
+        <v>598601</v>
       </c>
       <c r="R20" t="n">
-        <v>6942727</v>
+        <v>6942680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2887,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2897,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2929,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131194286</v>
+        <v>131194283</v>
       </c>
       <c r="B21" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,33 +2914,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2976,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598570</v>
+        <v>598603</v>
       </c>
       <c r="R21" t="n">
-        <v>6942714</v>
+        <v>6942663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3011,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3021,7 +2991,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131194275</v>
+        <v>131194284</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,10 +3066,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598499</v>
+        <v>598593</v>
       </c>
       <c r="R22" t="n">
-        <v>6942841</v>
+        <v>6942660</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3126,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3136,7 +3111,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3168,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131194276</v>
+        <v>131194285</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3211,10 +3186,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>598566</v>
+        <v>598601</v>
       </c>
       <c r="R23" t="n">
-        <v>6942801</v>
+        <v>6942696</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,7 +3221,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3256,12 +3231,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>färskt ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,10 +3263,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131194284</v>
+        <v>131194287</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,10 +3306,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>598593</v>
+        <v>598559</v>
       </c>
       <c r="R24" t="n">
-        <v>6942660</v>
+        <v>6942723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3366,7 +3341,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3376,7 +3351,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3408,10 +3383,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131194255</v>
+        <v>131194288</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3419,34 +3394,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>598556</v>
+        <v>598546</v>
       </c>
       <c r="R25" t="n">
-        <v>6942987</v>
+        <v>6942727</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3478,7 +3461,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3488,7 +3471,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,10 +3503,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131194272</v>
+        <v>131194290</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3548,7 +3536,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3558,10 +3546,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>598518</v>
+        <v>598460</v>
       </c>
       <c r="R26" t="n">
-        <v>6942861</v>
+        <v>6942693</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3593,7 +3581,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3603,12 +3591,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Typiskt bohål av tretåig hackspett. 1.5 meter ovan mark i gran. Innerdiametern omkring 4,5 cm vilket mättes med måttband.</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3635,45 +3623,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131194289</v>
+        <v>131194291</v>
       </c>
       <c r="B27" t="n">
-        <v>75367</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598468</v>
+        <v>598491</v>
       </c>
       <c r="R27" t="n">
-        <v>6942694</v>
+        <v>6942633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3705,7 +3701,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3715,7 +3711,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall. hela stammen full</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3739,6 +3740,245 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131194292</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Starrmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>598490</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6942625</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131194286</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Starrmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>598570</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6942714</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3598-2026 artfynd.xlsx
+++ b/artfynd/A 3598-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194289</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194293</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194254</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194268</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194269</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194270</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1700,6 +1745,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194271</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1820,6 +1870,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194272</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194273</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2060,6 +2120,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194274</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194275</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2300,6 +2370,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194276</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2420,6 +2495,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194277</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2540,6 +2620,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194278</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2660,6 +2745,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194279</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2780,6 +2870,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194280</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2900,6 +2995,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194282</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3020,6 +3120,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194283</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3140,6 +3245,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194284</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3260,6 +3370,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194285</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3380,6 +3495,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194287</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3500,6 +3620,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194288</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3620,6 +3745,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194290</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3740,6 +3870,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194291</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3860,6 +3995,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194292</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3979,8 +4119,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>